--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.07.2026 19:12</t>
+          <t>23.07.2026 19:36</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -601,6 +601,68 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Anteil der Fraktionen an allen Initiativen</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Initiativen'!G4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Initiativen'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Initiativen'!$G$5:$G$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showCatName val="1"/>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Bahnpolitische Drucksachen je Quartal</a:t>
             </a:r>
           </a:p>
@@ -846,7 +908,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -950,7 +1012,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1072,7 +1134,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1218,7 +1280,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1433,6 +1495,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2220,7 +2304,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.07.2026 20:13 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.07.2026 20:22 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -623,19 +623,78 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1AA037"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="009EE0"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="BE3075"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'Initiativen'!$A$5:$A$9</f>
+              <f>'Initiativen'!$A$5:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Initiativen'!$G$5:$G$9</f>
+              <f>'Initiativen'!$G$5:$G$8</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
           <showCatName val="1"/>
+          <showSerName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -682,6 +741,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1A1A1A"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -706,6 +768,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1AA037"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -730,6 +795,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="009EE0"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -754,6 +822,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BE3075"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -778,6 +849,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9E9E9E"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -802,6 +876,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5A6B7B"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -826,6 +903,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="B9BFC6"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1312,6 +1392,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4CAF50"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1336,6 +1419,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="D32F2F"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1360,6 +1446,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FBC02D"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1993,7 +2082,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2013,7 +2102,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2093,7 +2182,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2113,7 +2202,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -2304,7 +2393,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.07.2026 20:22 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.07.2026 20:32 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Themen" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Antwortzeiten" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Abstimmungen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Profil" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drucksachen'!$A$1:$O$283</definedName>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +106,30 @@
       <color rgb="00404040"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A0A0A0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00606060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001D3C6E"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -155,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,6 +225,11 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -327,6 +357,203 @@
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Fraktionsprofil im Vergleich (100 = Spitzenwert)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <radarChart>
+        <radarStyle val="marker"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Profil'!B12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profil'!$A$13:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profil'!$B$13:$B$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Profil'!C12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1AA037"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profil'!$A$13:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profil'!$C$13:$C$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Profil'!D12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="009EE0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profil'!$A$13:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profil'!$D$13:$D$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Profil'!E12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="BE3075"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profil'!$A$13:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profil'!$E$13:$E$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </radarChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
     </plotArea>
     <legend>
       <legendPos val="r"/>
@@ -1744,6 +1971,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2393,7 +2647,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.07.2026 20:32 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.07.2026 20:36 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
@@ -26437,4 +26691,1296 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="10" max="10"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Fraktionsprofil: vier messbare Dimensionen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Achtung Interpretation: Das sind Aktivitaetsmasse, kein Qualitaetsurteil. Ob eine Anfrage sachkundig oder blosse Symbolpolitik ist, steht in DIP nicht drin und laesst sich aus Metadaten nicht ableiten. Ausserdem koennen Regierungsfraktionen strukturell kaum Kleine Anfragen stellen - niedrige Werte heissen dort nicht Untaetigkeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>CDU/CSU</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Gruene</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>AfD</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Linke</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Was sie misst</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Hilfsraster Themen</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>CDU/CSU</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
+          <t>Gruene</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>AfD</t>
+        </is>
+      </c>
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t>Linke</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Initiativen gesamt</t>
+        </is>
+      </c>
+      <c r="B5" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Kleine Anfrage")+COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="C5" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Kleine Anfrage")+COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Kleine Anfrage")+COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Kleine Anfrage")+COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Wie viel eine Fraktion ueberhaupt einbringt</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>Bahnhoefe</t>
+        </is>
+      </c>
+      <c r="I5" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H5,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H5,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H5,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H5,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>davon abstimmungsfaehig</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,I$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,J$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,K$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Antrag")+COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Entschließungsantrag")+COUNTIFS(Drucksachen!$F$2:$F$283,L$4,Drucksachen!$E$2:$E$283,"Gesetzentwurf")</f>
+        <v/>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>Gestaltung statt blosser Kontrolle: Antraege und Gesetzentwuerfe</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Sicherheit</t>
+        </is>
+      </c>
+      <c r="I6" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H6,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H6,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H6,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H6,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Themenbreite</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>SUM(I$5:I$17)</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
+        <f>SUM(J$5:J$17)</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>SUM(K$5:K$17)</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>SUM(L$5:L$17)</f>
+        <v/>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>Wie viele der 13 Sachthemen beruehrt werden</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="I7" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H7,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H7,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H7,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H7,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Aktive Quartale</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>SUM(I$20:I$39)</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
+        <f>SUM(J$20:J$39)</f>
+        <v/>
+      </c>
+      <c r="D8" s="18">
+        <f>SUM(K$20:K$39)</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>SUM(L$20:L$39)</f>
+        <v/>
+      </c>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>Beharrlichkeit: Quartale mit Aktivitaet, von 20</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>Infrastruktur/Netz</t>
+        </is>
+      </c>
+      <c r="I8" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H8,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H8,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H8,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H8,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Konzernstruktur/DB AG</t>
+        </is>
+      </c>
+      <c r="I9" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H9,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H9,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H9,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H9,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>Finanzierung</t>
+        </is>
+      </c>
+      <c r="I10" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H10,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H10,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H10,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H10,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Normiert (Spitzenreiter je Zeile = 100)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Barrierefreiheit</t>
+        </is>
+      </c>
+      <c r="I11" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H11,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H11,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H11,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L11" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H11,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>CDU/CSU</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Gruene</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>AfD</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Linke</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>Deutschlandticket</t>
+        </is>
+      </c>
+      <c r="I12" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H12,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H12,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H12,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L12" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H12,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Initiativen gesamt</t>
+        </is>
+      </c>
+      <c r="B13" s="18">
+        <f>IFERROR(ROUND(B5/MAX($B$5:$E$5)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="18">
+        <f>IFERROR(ROUND(C5/MAX($B$5:$E$5)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="18">
+        <f>IFERROR(ROUND(D5/MAX($B$5:$E$5)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>IFERROR(ROUND(E5/MAX($B$5:$E$5)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Puenktlichkeit/Qualitaet</t>
+        </is>
+      </c>
+      <c r="I13" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H13,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J13" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H13,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H13,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L13" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H13,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>davon abstimmungsfaehig</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>IFERROR(ROUND(B6/MAX($B$6:$E$6)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="C14" s="18">
+        <f>IFERROR(ROUND(C6/MAX($B$6:$E$6)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>IFERROR(ROUND(D6/MAX($B$6:$E$6)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>IFERROR(ROUND(E6/MAX($B$6:$E$6)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>Nahverkehr/SPNV</t>
+        </is>
+      </c>
+      <c r="I14" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H14,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J14" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H14,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H14,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L14" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H14,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Themenbreite</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>IFERROR(ROUND(B7/MAX($B$7:$E$7)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="18">
+        <f>IFERROR(ROUND(C7/MAX($B$7:$E$7)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>IFERROR(ROUND(D7/MAX($B$7:$E$7)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>IFERROR(ROUND(E7/MAX($B$7:$E$7)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>Deutschlandtakt/Fahrplan</t>
+        </is>
+      </c>
+      <c r="I15" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H15,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J15" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H15,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H15,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L15" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H15,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Aktive Quartale</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>IFERROR(ROUND(B8/MAX($B$8:$E$8)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f>IFERROR(ROUND(C8/MAX($B$8:$E$8)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>IFERROR(ROUND(D8/MAX($B$8:$E$8)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>IFERROR(ROUND(E8/MAX($B$8:$E$8)*100,0),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="I16" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H16,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J16" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H16,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H16,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L16" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H16,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Gueterverkehr</t>
+        </is>
+      </c>
+      <c r="I17" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H17,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=I$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J17" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H17,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=J$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H17,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=K$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L17" s="18">
+        <f>IF(SUMPRODUCT(ISNUMBER(SEARCH($H17,Drucksachen!$I$2:$I$283))*(Drucksachen!$F$2:$F$283=L$4))&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>Hilfsraster Quartale</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>2021-Q4</t>
+        </is>
+      </c>
+      <c r="I20" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H20,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J20" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H20,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H20,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L20" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H20,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>2022-Q1</t>
+        </is>
+      </c>
+      <c r="I21" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H21,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H21,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H21,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H21,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>2022-Q2</t>
+        </is>
+      </c>
+      <c r="I22" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H22,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H22,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H22,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H22,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>2022-Q3</t>
+        </is>
+      </c>
+      <c r="I23" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H23,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H23,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H23,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H23,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>2022-Q4</t>
+        </is>
+      </c>
+      <c r="I24" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H24,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H24,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H24,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L24" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H24,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+      <c r="I25" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H25,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J25" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H25,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H25,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H25,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+      <c r="I26" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H26,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H26,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H26,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H26,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+      <c r="I27" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H27,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J27" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H27,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H27,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H27,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+      <c r="I28" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H28,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J28" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H28,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H28,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H28,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+      <c r="I29" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H29,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H29,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H29,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H29,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="I30" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H30,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H30,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H30,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H30,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="I31" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H31,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H31,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H31,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H31,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="I32" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H32,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J32" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H32,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H32,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L32" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H32,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="I33" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H33,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J33" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H33,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H33,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L33" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H33,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="I34" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H34,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H34,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K34" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H34,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L34" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H34,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="n"/>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="I35" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H35,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J35" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H35,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K35" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H35,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L35" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H35,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="I36" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H36,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J36" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H36,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K36" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H36,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L36" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H36,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="I37" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H37,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J37" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H37,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H37,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L37" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H37,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="I38" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H38,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J38" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H38,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K38" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H38,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L38" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H38,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="I39" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H39,Drucksachen!$F$2:$F$283,I$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="J39" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H39,Drucksachen!$F$2:$F$283,J$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="K39" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H39,Drucksachen!$F$2:$F$283,K$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+      <c r="L39" s="18">
+        <f>IF(COUNTIFS(Drucksachen!$C$2:$C$283,$H39,Drucksachen!$F$2:$F$283,L$4)&gt;0,1,0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2647,7 +2647,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.07.2026 20:36 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 24.07.2026 07:09 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -2647,7 +2647,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 24.07.2026 07:09 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 25.07.2026 06:39 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -2647,7 +2647,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 25.07.2026 06:39 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 26.07.2026 01:30 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 26.07.2026 02:37 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 26.07.2026 07:12 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 26.07.2026 07:12 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 27.07.2026 08:03 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 27.07.2026 08:03 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 28.07.2026 07:16 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 28.07.2026 07:16 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 29.07.2026 07:21 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 29.07.2026 07:21 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 30.07.2026 07:15 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 30.07.2026 07:15 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 31.07.2026 07:23 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 31.07.2026 07:23 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 01.08.2026 07:04 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 01.08.2026 07:04 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 02.08.2026 07:08 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O5">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 02.08.2026 07:08 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 03.08.2026 07:58 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2869,7 +2869,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Antwort</t>
+          <t>Kleine Anfrage</t>
         </is>
       </c>
       <c r="O4">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Kleine Anfrage</t>
+          <t>Antwort</t>
         </is>
       </c>
       <c r="O5">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 03.08.2026 07:58 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 04.08.2026 07:15 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 06.08.2026 07:17 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 07.08.2026 05:57 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 07.08.2026 05:57 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 08.08.2026 05:21 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 08.08.2026 05:21 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 09.08.2026 05:29 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 09.08.2026 05:29 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 10.08.2026 05:56 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 10.08.2026 05:56 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 11.08.2026 05:36 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 11.08.2026 05:36 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 12.08.2026 05:57 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 12.08.2026 05:57 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 13.08.2026 05:59 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 13.08.2026 05:59 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 14.08.2026 05:58 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 14.08.2026 05:58 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 15.08.2026 04:58 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 15.08.2026 04:58 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 16.08.2026 05:02 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 16.08.2026 05:02 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 17.08.2026 05:10 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 18.08.2026 05:03 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 19.08.2026 05:03 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>Ersatz von Brücken auf der Bahnstrecke Köln - Siegen (Siegstrecke)</t>
+          <t>Ersatz von Brücken auf der Bahnstrecke Köln-Siegen (Siegstrecke)</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 19.08.2026 05:03 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 20.08.2026 05:05 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 20.08.2026 05:05 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 21.08.2026 05:05 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 21.08.2026 05:05 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 22.08.2026 05:00 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 22.08.2026 05:00 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 23.08.2026 05:03 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 23.08.2026 05:03 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 24.08.2026 05:13 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 24.08.2026 05:13 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 25.08.2026 05:06 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 26.08.2026 05:06 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 27.08.2026 15:25 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 27.08.2026 15:25 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 28.08.2026 16:51 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 28.08.2026 16:51 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 29.08.2026 11:19 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 29.08.2026 11:19 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 30.08.2026 10:04 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 31.08.2026 11:04 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 01.09.2026 09:33 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 01.09.2026 09:33 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 02.09.2026 08:58 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 02.09.2026 08:58 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 03.09.2026 09:06 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>

--- a/bahnpolitik_gesamt.xlsx
+++ b/bahnpolitik_gesamt.xlsx
@@ -2969,7 +2969,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wahlvorschlag</t>
+          <t>Gesetzentwurf</t>
         </is>
       </c>
       <c r="O9">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Gesetzentwurf</t>
+          <t>Wahlvorschlag</t>
         </is>
       </c>
       <c r="O10">
@@ -3180,7 +3180,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>• Erstellt am 04.09.2026 08:59 durch bahnpolitik_dip.py Version 3.</t>
+          <t>• Erstellt am 05.09.2026 08:31 durch bahnpolitik_dip.py Version 3.</t>
         </is>
       </c>
     </row>
